--- a/dados/excel/municipio_cargo.xlsx
+++ b/dados/excel/municipio_cargo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$21</definedName>
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/municipio_cargo.xlsx
+++ b/dados/excel/municipio_cargo.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         <v>2572.32</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>95.37</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="3">
@@ -896,7 +896,7 @@
         <v>12503.93</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>96.26000000000001</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="4">
@@ -923,7 +923,7 @@
         <v>4778.01</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>92.67</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +950,7 @@
         <v>7336.12</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>78.95999999999999</v>
+        <v>79.27</v>
       </c>
     </row>
     <row r="6">
@@ -977,7 +977,7 @@
         <v>4876.53</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>96.59999999999999</v>
+        <v>96.76000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1004,7 +1004,7 @@
         <v>4587.47</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>58.67</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="8">
@@ -1031,7 +1031,7 @@
         <v>1084.8</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>76.51000000000001</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +1058,7 @@
         <v>5569.57</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>73.53</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="10">
@@ -1085,7 +1085,7 @@
         <v>6526.29</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>19.64</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="11">
@@ -1112,7 +1112,7 @@
         <v>18601.17</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>46.4</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="12">
@@ -1139,7 +1139,7 @@
         <v>13918.4</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>88.81</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1166,7 +1166,7 @@
         <v>12184.47</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>64.2</v>
+        <v>64.31</v>
       </c>
     </row>
     <row r="14">
@@ -1193,7 +1193,7 @@
         <v>4156.02</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>62.71</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="15">
@@ -1247,7 +1247,7 @@
         <v>5212.8</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>56.46</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="17">
@@ -1328,7 +1328,7 @@
         <v>15452.79</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>44.72</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="20">
